--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,53 +922,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62127640</v>
+        <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>106414</v>
+        <v>110070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221447</v>
+        <v>220204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mjösjö 1:85, Jmt</t>
+          <t>Mjösjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513392</v>
+        <v>513516</v>
       </c>
       <c r="R4" t="n">
-        <v>6989854</v>
+        <v>6989963</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,17 +995,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2004-08-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2004-08-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Detalj. 9 ex. inom 2x1 m. Sen Fältgentiana. Mjösjö 1:85, norr om gamla landsvägen, ca 40 m nordnordväst om bostadshuset på Mjösjö 1:85, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön, dellokal 3</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,35 +1009,35 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Gräsmatta på gårdsplan. Något sluttande,frisk gräsmark.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Norell</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62127640</t>
+          <t>https://artportalen.se/Sighting/136929224</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62127641</v>
+        <v>62127640</v>
       </c>
       <c r="B5" t="n">
         <v>106414</v>
@@ -1065,7 +1063,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513406</v>
+        <v>513392</v>
       </c>
       <c r="R5" t="n">
-        <v>6989861</v>
+        <v>6989854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,17 +1107,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2004-08-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2004-08-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Detalj. 1 ex, nyfynd vid NÖ husknuten. Mjösjö 1:85, norr om gamla landsvägen, ca 40 m nordnordväst om bostadshuset på Mjösjö 1:85, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön, dellokal 3</t>
+          <t>Detalj. 9 ex. inom 2x1 m. Sen Fältgentiana. Mjösjö 1:85, norr om gamla landsvägen, ca 40 m nordnordväst om bostadshuset på Mjösjö 1:85, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön, dellokal 3</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1131,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Gräsmatta på gårdsplan.</t>
+          <t>Gräsmatta på gårdsplan. Något sluttande,frisk gräsmark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1144,19 +1142,19 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Zetterström, Elisabet Zetterström</t>
+          <t>Bo Norell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62127641</t>
+          <t>https://artportalen.se/Sighting/62127640</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62127643</v>
+        <v>62127641</v>
       </c>
       <c r="B6" t="n">
         <v>106414</v>
@@ -1182,7 +1180,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1196,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513412</v>
+        <v>513406</v>
       </c>
       <c r="R6" t="n">
-        <v>6989839</v>
+        <v>6989861</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,17 +1224,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2004-08-17</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2004-08-17</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Detalj. 15 ex. inom 15x6 m. Sen Fältgentiana. Mjösjö 1:85, ca 10 m sydväst om bostadshuset, norr om gamla landsvägen, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön</t>
+          <t>Detalj. 1 ex, nyfynd vid NÖ husknuten. Mjösjö 1:85, norr om gamla landsvägen, ca 40 m nordnordväst om bostadshuset på Mjösjö 1:85, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön, dellokal 3</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1248,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Slåttermark på gårdstomt. Något, sluttande, torr-frisk mark. Öppet med stenblock.</t>
+          <t>Gräsmatta på gårdsplan.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1261,11 +1259,128 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Norell</t>
+          <t>Henrik Zetterström, Elisabet Zetterström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62127641</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>62127643</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mjösjö 1:85, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>513412</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6989839</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2004-08-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2004-08-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Detalj. 15 ex. inom 15x6 m. Sen Fältgentiana. Mjösjö 1:85, ca 10 m sydväst om bostadshuset, norr om gamla landsvägen, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Slåttermark på gårdstomt. Något, sluttande, torr-frisk mark. Öppet med stenblock.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/62127643</t>
         </is>
@@ -1278,6 +1393,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136929224</v>
       </c>
       <c r="B4" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
